--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29DB3528-EC37-468A-9AC4-54316330161A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80A3C0B4-72DB-4689-894B-C62C59567130}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37F9D8E3-949B-4656-9F25-07A2B59D37E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCC25267-A4CF-44E0-9F25-501ECEB3E570}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94C38A05-45E8-4859-A6DB-F2BF03BB6B03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66516B03-2296-43E7-BFE0-4B5D22654293}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80A3C0B4-72DB-4689-894B-C62C59567130}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34129939-F0E9-4F87-A08F-8EB388F83C83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCC25267-A4CF-44E0-9F25-501ECEB3E570}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A06C5B2-CED4-4A56-BB0C-ABBFA100E65E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66516B03-2296-43E7-BFE0-4B5D22654293}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CCE7EE-2361-419E-B53F-87B182407C46}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34129939-F0E9-4F87-A08F-8EB388F83C83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EBB6D2C-1CF8-4E40-A3C2-416245EE3767}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A06C5B2-CED4-4A56-BB0C-ABBFA100E65E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ADD2E1E-6D36-461C-B0E6-3D8291F01A3C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CCE7EE-2361-419E-B53F-87B182407C46}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D7E9A31-E65A-4BA6-B536-3675E1762625}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3954,13 +3954,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EBB6D2C-1CF8-4E40-A3C2-416245EE3767}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B75B0B0C-1004-4E12-8B3D-FE97CC0DBDC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1ADD2E1E-6D36-461C-B0E6-3D8291F01A3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C14561C6-3B09-48FF-B2F4-82907309A5B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D7E9A31-E65A-4BA6-B536-3675E1762625}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE29615-F660-4F93-8453-A27DA40F5F59}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06FC43D3-E67E-4638-8326-2B00D4435BAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B760E032-45DA-4538-A9BE-0BDE3A85D8D6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA6D621B-AC39-49DE-B7DB-5042F67B9850}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCBDBD4-C45B-488D-BD50-30F83CDB1820}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3578BBB9-6E8B-462E-AD78-360DDC180B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49029BA1-B8F2-4C9D-809C-CAFD59DCBE1E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B760E032-45DA-4538-A9BE-0BDE3A85D8D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C797906-6396-41C9-BC3A-B603986B4D80}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCBDBD4-C45B-488D-BD50-30F83CDB1820}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A51B66B-142E-443A-B6DB-C80B6DB2D0FF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49029BA1-B8F2-4C9D-809C-CAFD59DCBE1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BC6D95-A217-487B-9255-A59C9FDE529B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,291 +3421,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C797906-6396-41C9-BC3A-B603986B4D80}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A51B66B-142E-443A-B6DB-C80B6DB2D0FF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BC6D95-A217-487B-9255-A59C9FDE529B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,4 +3421,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C11EC9-2514-4FF4-ACF1-72569FAE0182}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E35A83B-8DF2-408E-90C0-4760DA5C56F1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364A5E50-6754-43C6-B7BC-EBB5F6994327}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,291 +3421,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C11EC9-2514-4FF4-ACF1-72569FAE0182}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E35A83B-8DF2-408E-90C0-4760DA5C56F1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{364A5E50-6754-43C6-B7BC-EBB5F6994327}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,4 +3421,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17D80894-3B94-443B-828A-53FE638CFBB1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB8A505-A186-4793-A362-02EDF44E1D59}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D80B6913-529F-4C83-B803-F31773E0B25E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17D80894-3B94-443B-828A-53FE638CFBB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB7B2F7A-2F86-45D3-9CD9-F878374E7EB1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FB8A505-A186-4793-A362-02EDF44E1D59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80C6BB0-EDEA-4F01-8A0E-FF6DB675372B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D80B6913-529F-4C83-B803-F31773E0B25E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5556D081-CD0D-40EC-B4A2-D402825500FD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB7B2F7A-2F86-45D3-9CD9-F878374E7EB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B137328B-659D-4D22-ABC3-D36E25A33CAF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80C6BB0-EDEA-4F01-8A0E-FF6DB675372B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51ECD9AA-8E3D-4711-8FC6-EA8E2A732C18}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5556D081-CD0D-40EC-B4A2-D402825500FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2589F90-493E-43EC-936D-D44E0C1B067B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B137328B-659D-4D22-ABC3-D36E25A33CAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0583AD72-9936-4BC1-BF52-62A4661953C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51ECD9AA-8E3D-4711-8FC6-EA8E2A732C18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1937D2-0305-4110-BE52-61C27A8CF60D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2589F90-493E-43EC-936D-D44E0C1B067B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DF7520-485A-414E-A245-DC94D9C8BC17}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0583AD72-9936-4BC1-BF52-62A4661953C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1C843E-8BC1-41F2-9123-1F56FD07CE01}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B1937D2-0305-4110-BE52-61C27A8CF60D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172F17A1-D6C8-404A-90E0-BB66C44F1FC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83DF7520-485A-414E-A245-DC94D9C8BC17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC6A857F-1A18-446E-89EE-8300353E4B9E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1C843E-8BC1-41F2-9123-1F56FD07CE01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11857460-9EDC-4AAE-A4F4-66E0625172F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{172F17A1-D6C8-404A-90E0-BB66C44F1FC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26D389C7-1D1C-4D94-9112-AB361598BA0B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC6A857F-1A18-446E-89EE-8300353E4B9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14F61BB8-3D03-4DA1-B9AE-6909F22FAEA4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,291 +3421,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11857460-9EDC-4AAE-A4F4-66E0625172F9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26D389C7-1D1C-4D94-9112-AB361598BA0B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14F61BB8-3D03-4DA1-B9AE-6909F22FAEA4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,4 +3421,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88358AF6-931F-47E7-B879-51D5C904FC9E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E5665E-4440-48C9-A9F9-DA51C8649290}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0868A5DC-D9D2-442D-BAAC-EE2E2F871113}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88358AF6-931F-47E7-B879-51D5C904FC9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C6717A-195C-432A-9B47-EF1058286792}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69E5665E-4440-48C9-A9F9-DA51C8649290}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49053FA5-6DEA-461E-B3A5-FF24463DF2E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0868A5DC-D9D2-442D-BAAC-EE2E2F871113}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54902149-F65C-46C4-AC7F-23F1F89678A5}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C6717A-195C-432A-9B47-EF1058286792}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{940D4CCE-9110-4788-BD9F-DD3E6F7A664B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49053FA5-6DEA-461E-B3A5-FF24463DF2E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75D45A32-4E9B-484A-ABAA-31E2AA2FA446}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54902149-F65C-46C4-AC7F-23F1F89678A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AEF148-A623-49D4-B243-B13C7C81F75E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{940D4CCE-9110-4788-BD9F-DD3E6F7A664B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5829F2D5-CF21-4FD4-9411-9DAAC78FF4CC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75D45A32-4E9B-484A-ABAA-31E2AA2FA446}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C41D2B3-0DF1-486E-B0AC-7CA08990D196}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7AEF148-A623-49D4-B243-B13C7C81F75E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{567CF6D1-15D1-461A-A2C1-681F3F328EB4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5829F2D5-CF21-4FD4-9411-9DAAC78FF4CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454DEFA0-02F5-4C88-B4F1-A6C2A57CB087}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C41D2B3-0DF1-486E-B0AC-7CA08990D196}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87F92B1-1CF9-4DF1-A33F-63F000D716E0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{567CF6D1-15D1-461A-A2C1-681F3F328EB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE359E1B-4444-49BD-B77F-CB725E9DD48E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3699,13 +3699,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{454DEFA0-02F5-4C88-B4F1-A6C2A57CB087}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{205B7CEC-CCF6-4ED7-929E-C632D04A14FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C87F92B1-1CF9-4DF1-A33F-63F000D716E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6472B17-6813-49DF-A236-DDCACF02C060}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE359E1B-4444-49BD-B77F-CB725E9DD48E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31719717-CC7C-4236-A654-B6AC7F04A264}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,291 +3421,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{205B7CEC-CCF6-4ED7-929E-C632D04A14FA}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6472B17-6813-49DF-A236-DDCACF02C060}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31719717-CC7C-4236-A654-B6AC7F04A264}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
+++ b/____EvoM1_TraitTable/dexterity_corticospinaltract.xlsx
@@ -3421,4 +3421,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E129959D-5449-47DD-A689-8572F5222FDF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A73456B-EA58-4518-97BD-B1624896F57A}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A831D082-B382-46A3-8149-0E99562B48D0}"/>
 </file>